--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_110_R11.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_110_R11.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3504</v>
+        <v>5.3414</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8583</v>
+        <v>7.0509</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5079</v>
+        <v>-1.7095</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2699</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3075</v>
+        <v>-0.3165</v>
       </c>
       <c r="T2" t="n">
-        <v>0.362</v>
+        <v>0.5546</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6695</v>
+        <v>-0.8711</v>
       </c>
       <c r="V2" t="n">
         <v>2.6805</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1322</v>
+        <v>2.6715</v>
       </c>
       <c r="E3" t="n">
-        <v>2.514</v>
+        <v>3.3644</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6183</v>
+        <v>-0.6929</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6078</v>
+        <v>3.7967</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0226</v>
+        <v>0.1164</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4148</v>
+        <v>3.6804</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6981</v>
+        <v>5.9456</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2637</v>
+        <v>2.2084</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5655</v>
+        <v>3.7371</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0903</v>
+        <v>-2.1488</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.241</v>
+        <v>-2.0921</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1507</v>
+        <v>-0.0568</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2473</v>
+        <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3673</v>
+        <v>-0.6614</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8338</v>
+        <v>0.362</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4665</v>
+        <v>-1.0233</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4362</v>
+        <v>2.6097</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3644</v>
+        <v>1.9242</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9282</v>
+        <v>0.6855</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7967</v>
+        <v>1.6078</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1164</v>
+        <v>2.0226</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6804</v>
+        <v>-0.4148</v>
       </c>
       <c r="J4" t="n">
-        <v>5.9456</v>
+        <v>2.6981</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2084</v>
+        <v>3.2637</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7371</v>
+        <v>-0.5655</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1488</v>
+        <v>-1.0903</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0921</v>
+        <v>-1.241</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0568</v>
+        <v>0.1507</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0154</v>
+        <v>3.2473</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8966</v>
+        <v>-0.1553</v>
       </c>
       <c r="T4" t="n">
-        <v>0.362</v>
+        <v>0.244</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2586</v>
+        <v>-0.3993</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8427</v>
+        <v>1.1515</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0556</v>
+        <v>0.2299</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7872</v>
+        <v>0.9216</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2117</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4462</v>
+        <v>0.7549</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0657</v>
+        <v>0.2401</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3804</v>
+        <v>0.5149</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2218</v>
+        <v>0.4015</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0662</v>
+        <v>-0.4765</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8444</v>
+        <v>0.878</v>
       </c>
       <c r="G6" t="n">
         <v>2.1862</v>
@@ -922,13 +922,13 @@
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5988</v>
+        <v>0.0246</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8136</v>
+        <v>-0.2238</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2148</v>
+        <v>0.2484</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5773</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ATAMNA</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5104</v>
+        <v>-1.444</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9021</v>
+        <v>1.6414</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6083</v>
+        <v>-3.0854</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2784</v>
+        <v>-1.1661</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6494</v>
+        <v>-2.8559</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6291</v>
+        <v>1.6898</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7527</v>
+        <v>2.1188</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0336</v>
+        <v>-0.6281</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7863</v>
+        <v>2.7469</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-3.2849</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-2.2278</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1573</v>
+        <v>-1.0572</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4639</v>
+        <v>-0.3449</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1494</v>
+        <v>-0.1373</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3145</v>
+        <v>-0.2076</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.3247</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>A. ATAMNA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7032</v>
+        <v>-1.5104</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6847</v>
+        <v>-0.9021</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3879</v>
+        <v>-0.6083</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1661</v>
+        <v>-1.2784</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.8559</v>
+        <v>-0.6494</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6898</v>
+        <v>-0.6291</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1188</v>
+        <v>-0.7527</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6281</v>
+        <v>0.0336</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7469</v>
+        <v>-0.7863</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.2849</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2278</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0572</v>
+        <v>0.1573</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5515</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.604</v>
+        <v>-0.4639</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.094</v>
+        <v>-0.1494</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.51</v>
+        <v>-0.3145</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3247</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9383</v>
+        <v>-1.7457</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5877</v>
+        <v>-2.3951</v>
       </c>
       <c r="F9" t="n">
         <v>0.6494</v>
@@ -1156,10 +1156,10 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3971</v>
+        <v>-0.2045</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5149</v>
+        <v>-0.3222</v>
       </c>
       <c r="U9" t="n">
         <v>0.1177</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5066</v>
+        <v>-2.196</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3074</v>
+        <v>-1.9968</v>
       </c>
       <c r="F10" t="n">
         <v>-0.1991</v>
@@ -1234,10 +1234,10 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8531</v>
+        <v>-0.5425</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.731</v>
+        <v>-0.4204</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1221</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1041</v>
+        <v>-3.1289</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.143</v>
+        <v>-4.5965</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0389</v>
+        <v>1.4676</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0416</v>
@@ -1312,13 +1312,13 @@
         <v>2.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0277</v>
+        <v>0.0029</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6721</v>
+        <v>-0.1256</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6998</v>
+        <v>0.1285</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3943</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7771</v>
+        <v>2.150600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4706</v>
+        <v>3.843800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6932</v>
+        <v>-1.6931</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2675</v>
+        <v>-1.267499999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-4.664199999999999</v>
@@ -1369,7 +1369,7 @@
         <v>6.744299999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>4.4994</v>
+        <v>4.499400000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-12.5112</v>
@@ -1381,7 +1381,7 @@
         <v>-1.1031</v>
       </c>
       <c r="P12" t="n">
-        <v>5.798799999999999</v>
+        <v>5.798800000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.9173</v>
@@ -1390,13 +1390,13 @@
         <v>19.7161</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2798</v>
+        <v>-1.9066</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3514999999999999</v>
+        <v>0.02200000000000008</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.9285</v>
+        <v>-1.9284</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4740000000000003</v>
@@ -1405,13 +1405,13 @@
         <v>6.4953</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.969300000000001</v>
+        <v>-6.9693</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.371</v>
+        <v>4.2475</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7431</v>
+        <v>4.9652</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6279</v>
+        <v>-0.7177</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0609</v>
+        <v>5.8474</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9773</v>
+        <v>2.7658</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0837</v>
+        <v>3.0816</v>
       </c>
       <c r="J13" t="n">
-        <v>4.0558</v>
+        <v>8.010300000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1257</v>
+        <v>3.7678</v>
       </c>
       <c r="L13" t="n">
-        <v>0.93</v>
+        <v>4.2425</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9948</v>
+        <v>-2.1629</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1484</v>
+        <v>-1.002</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8464</v>
+        <v>-1.1609</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.5515</v>
+        <v>-3.7112</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4519</v>
+        <v>0.0934</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2388</v>
+        <v>0.13</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2131</v>
+        <v>-0.0367</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1418</v>
+        <v>0.3943</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X13" t="n">
         <v>-0.1418</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4624</v>
+        <v>2.9443</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0216</v>
+        <v>2.0354</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5592</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>5.8474</v>
+        <v>2.0609</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7658</v>
+        <v>1.9773</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0816</v>
+        <v>0.0837</v>
       </c>
       <c r="J14" t="n">
-        <v>8.010300000000001</v>
+        <v>4.0558</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7678</v>
+        <v>3.1257</v>
       </c>
       <c r="L14" t="n">
-        <v>4.2425</v>
+        <v>0.93</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1629</v>
+        <v>-1.9948</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.002</v>
+        <v>-1.1484</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1609</v>
+        <v>-0.8464</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.0876</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.7112</v>
+        <v>-2.5515</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6917</v>
+        <v>1.0251</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8136</v>
+        <v>0.5311</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8782</v>
+        <v>0.494</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-0.1418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9785</v>
+        <v>1.0235</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0609</v>
+        <v>-0.175</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9175</v>
+        <v>1.1985</v>
       </c>
       <c r="G15" t="n">
         <v>1.3158</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7323</v>
+        <v>0.7773</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7196</v>
+        <v>0.4837</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0127</v>
+        <v>0.2937</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1078</v>
+        <v>0.2074</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2892</v>
+        <v>0.5251</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.397</v>
+        <v>-0.3177</v>
       </c>
       <c r="G16" t="n">
         <v>-2.4017</v>
@@ -1702,13 +1702,13 @@
         <v>2.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0593</v>
+        <v>0.3745</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2513</v>
+        <v>-0.0154</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3106</v>
+        <v>0.3899</v>
       </c>
       <c r="V16" t="n">
         <v>2.0026</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3084</v>
+        <v>0.1425</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2081</v>
+        <v>-0.5003</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8996</v>
+        <v>0.6428</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1167</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3264</v>
+        <v>0.7773</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7468</v>
+        <v>-0.0391</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0732</v>
+        <v>0.8164</v>
       </c>
       <c r="V17" t="n">
         <v>-1.214</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1019</v>
+        <v>-1.0175</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5061</v>
+        <v>-0.3882</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5957</v>
+        <v>-0.6294</v>
       </c>
       <c r="G18" t="n">
         <v>-2.5588</v>
@@ -1858,13 +1858,13 @@
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3668</v>
+        <v>0.4512</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1766</v>
+        <v>-0.0587</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5434</v>
+        <v>0.5098</v>
       </c>
       <c r="V18" t="n">
         <v>0.3943</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MILTON</t>
+          <t>N. CALATHES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3452</v>
+        <v>-2.4384</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9542</v>
+        <v>-2.3994</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.391</v>
+        <v>-0.039</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.7452</v>
+        <v>0.8659</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2185</v>
+        <v>-0.0108</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.5267</v>
+        <v>0.8767</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.1005</v>
+        <v>1.4807</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8976</v>
+        <v>0.39</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.9982</v>
+        <v>1.0907</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6447</v>
+        <v>-0.6148</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1161</v>
+        <v>-0.4008</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5286</v>
+        <v>-0.214</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.3195</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4793</v>
+        <v>-3.7112</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8587</v>
+        <v>-0.1445</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4812</v>
+        <v>-0.1689</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6225000000000001</v>
+        <v>0.0244</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8608</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. CALATHES</t>
+          <t>S. MILTON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1176</v>
+        <v>-2.9192</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7533</v>
+        <v>-2.3696</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3643</v>
+        <v>-0.5495</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8659</v>
+        <v>-3.7452</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0108</v>
+        <v>-0.2185</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8767</v>
+        <v>-3.5267</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4807</v>
+        <v>-2.1005</v>
       </c>
       <c r="K21" t="n">
-        <v>0.39</v>
+        <v>0.8976</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0907</v>
+        <v>-2.9982</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6148</v>
+        <v>-1.6447</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4008</v>
+        <v>-1.1161</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.214</v>
+        <v>-0.5286</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0876</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.7112</v>
+        <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8237</v>
+        <v>1.2847</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5228</v>
+        <v>1.0657</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3009</v>
+        <v>0.219</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>1.8608</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="22">
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7773</v>
+        <v>0.5817999999999985</v>
       </c>
       <c r="E22" t="n">
-        <v>1.693100000000001</v>
+        <v>1.693200000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4705</v>
+        <v>-1.1115</v>
       </c>
       <c r="G22" t="n">
-        <v>1.267600000000001</v>
+        <v>1.2676</v>
       </c>
       <c r="H22" t="n">
-        <v>4.664099999999999</v>
+        <v>4.6641</v>
       </c>
       <c r="I22" t="n">
         <v>-3.3964</v>
@@ -2149,7 +2149,7 @@
         <v>11.4083</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1027</v>
+        <v>1.102699999999999</v>
       </c>
       <c r="M22" t="n">
         <v>-11.2436</v>
@@ -2170,16 +2170,16 @@
         <v>13.9173</v>
       </c>
       <c r="S22" t="n">
-        <v>2.28</v>
+        <v>4.638999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9285</v>
+        <v>1.9284</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3513999999999999</v>
+        <v>2.7105</v>
       </c>
       <c r="V22" t="n">
-        <v>0.4739</v>
+        <v>0.4738999999999998</v>
       </c>
       <c r="W22" t="n">
         <v>6.9693</v>
